--- a/reports/一级子公司A_利润表_2025-12.xlsx
+++ b/reports/一级子公司A_利润表_2025-12.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>166739992</v>
+        <v>169692844</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>162492036</v>
+        <v>161742925</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>2018983738</v>
+        <v>2017410386</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>658232</v>
+        <v>662644</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>8225899</v>
+        <v>8231841</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>569952</v>
+        <v>574116</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>7135559</v>
+        <v>7144248</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>485561</v>
+        <v>485580</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>6046498</v>
+        <v>6055306</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>445369</v>
+        <v>445763</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>5562612</v>
+        <v>5570846</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>243522</v>
+        <v>241756</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>3023467</v>
+        <v>3027135</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>194193</v>
+        <v>193114</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>2419250</v>
+        <v>2421016</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>164143163</v>
+        <v>167089871</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>159895207</v>
+        <v>159139952</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>82327968</v>
+        <v>81521205</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>1023088681</v>
+        <v>1022026493</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>1507437</v>
+        <v>1498882</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>18768499</v>
+        <v>18740211</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>1355959</v>
+        <v>1358307</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>16949527</v>
+        <v>16924976</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>73107247</v>
+        <v>73112850</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>907555419</v>
+        <v>907051518</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1543473</v>
+        <v>1559992</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>19363122</v>
+        <v>19354782</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>679663</v>
+        <v>682566</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>8471119</v>
+        <v>8469519</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2411846</v>
+        <v>2436405</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>30249770</v>
+        <v>30265902</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>1065880</v>
+        <v>1071600</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>13306100</v>
+        <v>13317196</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>4158011</v>
+        <v>4182969</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>52005912</v>
+        <v>52069915</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>89945</v>
+        <v>90058</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>1079307</v>
+        <v>1081077</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>2207809</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>27610812</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>1469083</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>18403433</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>111452654</v>
+        <v>118333516</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>99604770</v>
+        <v>98571484</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>97567403</v>
+        <v>96541787</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>1210217498</v>
+        <v>1209486310</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>2037367</v>
+        <v>2029697</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>25420376</v>
+        <v>25392784</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>3680739</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>45940298</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>1180438</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>14700772</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>739299</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>9189318</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>888545</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>11030191</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>666933</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>8275565</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>444567</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>5519090</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>370097</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>4600727</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>1699478</v>
+        <v>1701343</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>21165733</v>
+        <v>21192276</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>1305154</v>
+        <v>1309682</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>16326594</v>
+        <v>16349493</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>1070192</v>
+        <v>1064982</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>13302815</v>
+        <v>13320855</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>8054678</v>
+        <v>8020764</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>100389730</v>
+        <v>100489948</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>351297</v>
+        <v>337840</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>4198797</v>
+        <v>4236277</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>672239</v>
+        <v>666485</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>8040148</v>
+        <v>8038850</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>761377</v>
+        <v>666485</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>9122032</v>
+        <v>8038850</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>90376</v>
+        <v>89704</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>1080524</v>
+        <v>1079123</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>341610</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>4099963</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>645740</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>8039572</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>228705</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>2733884</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>171781</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>2051080</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>286494</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>3419850</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>926102</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>11498642</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>152588</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>1825308</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>114235</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>1369281</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>189979</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>2282265</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>132699</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>1597398</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>94618</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>1140686</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>75616</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>912204</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>56703</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>683870</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>52690509</v>
+        <v>51050662</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>61112595</v>
+        <v>57084815</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>368287</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>4593949</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>95129</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>1138919</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>149973</v>
+        <v>150494</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>1800935</v>
+        <v>1798661</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>52540536</v>
+        <v>51268455</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>5297611</v>
+        <v>5327893</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>63605537</v>
+        <v>63600673</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>47242925</v>
+        <v>45940562</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>47242925</v>
+        <v>45940562</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>47242925</v>
+        <v>45940562</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>47242925</v>
+        <v>45940562</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>47242925</v>
+        <v>45940562</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
